--- a/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
+++ b/inferences/jesuita-entrada-Coimbra-cargos_tarefas.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Funda uma residência</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Funda uma residência</t>
+          <t>Superior das Índias</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,17 +559,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Superior das Índias</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Resgata cativos portugueses</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,22 +623,22 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Resgata cativos portugueses</t>
+          <t>Provincial da Etiópia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provincial da Etiópia</t>
+          <t>Resgata cativos portugueses</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,22 +687,22 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Resgata cativos portugueses</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -719,22 +719,22 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Funda a missão de Kwangtung</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -751,22 +751,22 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Funda a missão de Kwangtung</t>
+          <t>Vice-provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vice-provincial das Índias Orientais</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Superior da China</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -847,27 +847,27 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Superior da China</t>
+          <t>Funda a residência jesuíta de Macau</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,27 +879,27 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Funda a residência jesuíta de Macau</t>
+          <t>Vice-provincial de Cochim</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,17 +911,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-francisco-perez</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Francisco Pérez</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vice-provincial de Cochim</t>
+          <t>Superior de Macau</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Superior de Macau</t>
+          <t>Funda a residência jesuíta de Macau</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -975,27 +975,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-perez</t>
+          <t>deh-belchior-nunes-barreto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Francisco Pérez</t>
+          <t>Belchior Nunes Barreto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Funda a residência jesuíta de Macau</t>
+          <t>Visitador da Província da Índia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-nunes-barreto</t>
+          <t>deh-goncalo-alvares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Belchior Nunes Barreto</t>
+          <t>Gonçalo Álvares</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Visitador da Província da Índia</t>
+          <t>Visitador das Índias e do Japão</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,27 +1039,27 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-alvares</t>
+          <t>deh-belchior-miguel-carneiro-leitao</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gonçalo Álvares</t>
+          <t>Belchior Miguel Carneiro Leitão</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Visitador das Índias e do Japão</t>
+          <t>Funda o hospital de Macau</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,17 +1071,17 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>deh-belchior-miguel-carneiro-leitao</t>
+          <t>deh-goncalo-alvares</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Belchior Miguel Carneiro Leitão</t>
+          <t>Gonçalo Álvares</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Funda o hospital de Macau</t>
+          <t>Manda abrir uma escola elementar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-alvares</t>
+          <t>deh-tiburcio-de-quadros</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gonçalo Álvares</t>
+          <t>Tibúrcio de Quadros</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Manda abrir uma escola elementar</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Superior da China</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1167,17 +1167,17 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>deh-tiburcio-de-quadros</t>
+          <t>deh-cristovao-da-costa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tibúrcio de Quadros</t>
+          <t>Cristóvão da Costa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Superior da China</t>
+          <t>Superior de Macau</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,17 +1199,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>deh-cristovao-da-costa</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cristóvão da Costa</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Superior de Macau</t>
+          <t>Monitor de Alessandro Valignano</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monitor de Alessandro Valignano</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,17 +1295,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-pedro-martins</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Pedro Martins</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Reitor de Goa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reitor de Goa</t>
+          <t>Provincial das Índias Orientais</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>deh-pedro-martins</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pedro Martins</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Provincial das Índias Orientais</t>
+          <t>Superior da residência de Macau</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Superior da residência de Macau</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,17 +1423,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,17 +1519,17 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-lourenco-mexia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Lourenço Mexia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Analista das missões da China e do Japão</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1583,27 +1583,27 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>deh-lourenco-mexia</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lourenço Mexia</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analista das missões da China e do Japão</t>
+          <t>Promotor da missão em África</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Promotor da missão em África</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,17 +1647,17 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-manuel-gaspar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Manuel Gaspar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Procurador da China e do Japão</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,22 +1679,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-gaspar</t>
+          <t>deh-sebastiao-fernandes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Manuel Gaspar</t>
+          <t>Sebastião Fernandes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Procurador da China e do Japão</t>
+          <t>Destinado à China</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-fernandes</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sebastião Fernandes</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Destinado à China</t>
+          <t>Mestre dos Noviços</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,22 +1743,22 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mestre dos Noviços</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,27 +1839,27 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-gaspar-ferreira</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Gaspar Ferreira</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Mestre dos Noviços</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,17 +1871,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-ferreira</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gaspar Ferreira</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mestre dos Noviços</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1903,17 +1903,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1935,22 +1935,22 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-vieira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Francisco Vieira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1967,22 +1967,22 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1999,27 +1999,27 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2063,22 +2063,22 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Reitor do Colégio de Macau</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2095,17 +2095,17 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-nicolau-pimenta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Nicolau Pimenta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reitor do Colégio de Macau</t>
+          <t>Visitador das Índias Orientais</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2127,17 +2127,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>deh-nicolau-pimenta</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nicolau Pimenta</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Visitador das Índias Orientais</t>
+          <t>Visitador das missões</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2159,17 +2159,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Visitador das missões</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2191,17 +2191,17 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-vieira</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Francisco Vieira</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Visitador das missões</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2223,17 +2223,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-vieira</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Vieira</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Visitador das missões</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2255,22 +2255,22 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-vieira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Francisco Vieira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Carta anual da China</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2287,27 +2287,27 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carta anual da China</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2319,17 +2319,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Visitador das províncias do Malabar</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2351,17 +2351,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Visitador das províncias do Malabar</t>
+          <t>Secretário da Congregação Provincial do Japão</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2383,27 +2383,27 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Secretário da Congregação Provincial do Japão</t>
+          <t>Carta anual da Cochichina de 1619</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2415,27 +2415,27 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Carta anual da Cochichina de 1619</t>
+          <t>Visitador das províncias do Malabar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Visitador das províncias do Malabar</t>
+          <t>Visitador das províncias de Goa e do Malabar</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2479,17 +2479,17 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Visitador das províncias de Goa e do Malabar</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2511,17 +2511,17 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2543,17 +2543,17 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-joao-da-rocha</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>João da Rocha</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Superior da missão da China</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-rocha</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>João da Rocha</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Superior da missão da China</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2607,17 +2607,17 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Superior da missão da China</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2639,22 +2639,22 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Superior da missão da China</t>
+          <t>Faz mais de 40000 baptismos no Tonquim</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2671,17 +2671,17 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Faz mais de 40000 baptismos no Tonquim</t>
+          <t>Carta anual da Cochichina de 1622</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2703,22 +2703,22 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Carta anual da Cochichina de 1622</t>
+          <t>Procurador da província</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2735,27 +2735,27 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Procurador da província</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2767,22 +2767,22 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Visitador de Agra</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Visitador de Agra</t>
+          <t>Superior de Agra</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2831,17 +2831,17 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-francisco-pacheco</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Francisco Pacheco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Superior de Agra</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,17 +2863,17 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pacheco</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Francisco Pacheco</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2895,22 +2895,22 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-joao-rodrigues-girao</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>João Rodrigues Girão</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Carta anual do Japão</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2927,22 +2927,22 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-rodrigues-girao</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>João Rodrigues Girão</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Carta anual do Japão</t>
+          <t>Visitador das províncias de Goa e do Malabar</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Visitador das províncias de Goa e do Malabar</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Preside a conferência de Kiating e mostra-se adversário do emprego de T'ien e Chang-ti para designar Deus</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3023,27 +3023,27 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Preside a conferência de Kiating e mostra-se adversário do emprego de T'ien e Chang-ti para designar Deus</t>
+          <t>Superior da missão do Tonquim</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,17 +3055,17 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Superior da missão do Tonquim</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3087,17 +3087,17 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-mateus-de-couros</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Mateus de Couros</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Provincial do Japão e da China</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-couros</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mateus de Couros</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Provincial do Japão e da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3151,17 +3151,17 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-antonio-de-andrade</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>António de Andrade</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Provincial de Goa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Provincial de Goa</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3215,17 +3215,17 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-andrade</t>
+          <t>deh-sebastiao-vieira</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>António de Andrade</t>
+          <t>Sebastião Vieira</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3247,17 +3247,17 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-vieira</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sebastião Vieira</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Vice-provincial da China do Norte</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3279,17 +3279,17 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-manuel-dias-o-novo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Manuel Dias, o Novo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Norte</t>
+          <t>Vice-provincial da China</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3311,17 +3311,17 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-dias-o-novo</t>
+          <t>deh-andre-palmeiro</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Manuel Dias, o Novo</t>
+          <t>André Palmeiro</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vice-provincial da China</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3343,27 +3343,27 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-palmeiro</t>
+          <t>deh-gabriel-de-magalhaes</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>André Palmeiro</t>
+          <t>Gabriel de Magalhães</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Visitador do Japão e da China</t>
+          <t>Ensinar Filosofia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>jesuita-cargo</t>
+          <t>jesuita-tarefa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3375,17 +3375,17 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-de-magalhaes</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gabriel de Magalhães</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ensinar Filosofia</t>
+          <t>Participa numa consulta sobre a China</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3407,27 +3407,27 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Participa numa consulta sobre a China</t>
+          <t>Vice-provincial da China do Norte</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>jesuita-tarefa</t>
+          <t>jesuita-cargo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Norte</t>
+          <t>Superior das seis residências do Norte</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3471,17 +3471,17 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-furtado</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Francisco Furtado</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Superior das seis residências do Norte</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3503,17 +3503,17 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Procurador da Vice-província da China</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3535,17 +3535,17 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-da-fonseca</t>
+          <t>deh-gaspar-do-amaral</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gonçalo da Fonseca</t>
+          <t>Gaspar do Amaral</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Procurador da Vice-província da China</t>
+          <t>Vice-provincial do Japão</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3567,17 +3567,17 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>deh-gaspar-do-amaral</t>
+          <t>deh-sebastiao-da-maia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Gaspar do Amaral</t>
+          <t>Sebastião da Maia</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vice-provincial do Japão</t>
+          <t>Provincial do Japão</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3599,17 +3599,17 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastiao-da-maia</t>
+          <t>deh-francisco-furtado</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sebastião da Maia</t>
+          <t>Francisco Furtado</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Provincial do Japão</t>
+          <t>Vice-provincial da China do Sul</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vice-provincial da China do Sul</t>
+          <t>Visitador do Japão e da China</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
